--- a/final_data_pipeline/output/311615longform.xlsx
+++ b/final_data_pipeline/output/311615longform.xlsx
@@ -912,7 +912,7 @@
         <v>117</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -995,7 +995,7 @@
         <v>117</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -1078,7 +1078,7 @@
         <v>117</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1161,7 +1161,7 @@
         <v>117</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1244,7 +1244,7 @@
         <v>117</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1327,7 +1327,7 @@
         <v>117</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1410,7 +1410,7 @@
         <v>117</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1493,7 +1493,7 @@
         <v>117</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1576,7 +1576,7 @@
         <v>117</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1659,7 +1659,7 @@
         <v>117</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1742,7 +1742,7 @@
         <v>117</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1825,7 +1825,7 @@
         <v>117</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -1908,7 +1908,7 @@
         <v>117</v>
       </c>
       <c r="AA14">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB14">
         <v>8000</v>
@@ -1991,7 +1991,7 @@
         <v>117</v>
       </c>
       <c r="AA15">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB15">
         <v>8000</v>
@@ -2074,7 +2074,7 @@
         <v>117</v>
       </c>
       <c r="AA16">
-        <v>10</v>
+        <v>17.25771604938272</v>
       </c>
       <c r="AB16">
         <v>8000</v>
@@ -2157,7 +2157,7 @@
         <v>117</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB17">
         <v>8000</v>
@@ -2240,7 +2240,7 @@
         <v>117</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2323,7 +2323,7 @@
         <v>117</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -2406,7 +2406,7 @@
         <v>117</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB20">
         <v>8000</v>
@@ -2489,7 +2489,7 @@
         <v>117</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB21">
         <v>8000</v>
@@ -2572,7 +2572,7 @@
         <v>117</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB22">
         <v>8000</v>
@@ -2655,7 +2655,7 @@
         <v>117</v>
       </c>
       <c r="AA23">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB23">
         <v>8000</v>
@@ -2738,7 +2738,7 @@
         <v>117</v>
       </c>
       <c r="AA24">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB24">
         <v>8000</v>
@@ -2821,7 +2821,7 @@
         <v>117</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AB25">
         <v>8000</v>
@@ -6141,7 +6141,7 @@
         <v>117</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6224,7 +6224,7 @@
         <v>117</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6307,7 +6307,7 @@
         <v>117</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -6390,7 +6390,7 @@
         <v>117</v>
       </c>
       <c r="AA68">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB68">
         <v>8000</v>
@@ -6473,7 +6473,7 @@
         <v>117</v>
       </c>
       <c r="AA69">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB69">
         <v>8000</v>
@@ -6556,7 +6556,7 @@
         <v>117</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -6639,7 +6639,7 @@
         <v>117</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -6722,7 +6722,7 @@
         <v>117</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -6805,7 +6805,7 @@
         <v>117</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -6888,7 +6888,7 @@
         <v>117</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -6971,7 +6971,7 @@
         <v>117</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7054,7 +7054,7 @@
         <v>117</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -7137,7 +7137,7 @@
         <v>117</v>
       </c>
       <c r="AA77">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB77">
         <v>8000</v>
@@ -7220,7 +7220,7 @@
         <v>117</v>
       </c>
       <c r="AA78">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB78">
         <v>8000</v>
@@ -7303,7 +7303,7 @@
         <v>117</v>
       </c>
       <c r="AA79">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB79">
         <v>8000</v>
@@ -7635,7 +7635,7 @@
         <v>117</v>
       </c>
       <c r="AA83">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB83">
         <v>8000</v>
@@ -7718,7 +7718,7 @@
         <v>117</v>
       </c>
       <c r="AA84">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB84">
         <v>8000</v>
@@ -7801,7 +7801,7 @@
         <v>117</v>
       </c>
       <c r="AA85">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB85">
         <v>8000</v>
@@ -7884,7 +7884,7 @@
         <v>117</v>
       </c>
       <c r="AA86">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB86">
         <v>8000</v>
@@ -7967,7 +7967,7 @@
         <v>117</v>
       </c>
       <c r="AA87">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB87">
         <v>8000</v>
@@ -8050,7 +8050,7 @@
         <v>117</v>
       </c>
       <c r="AA88">
-        <v>10</v>
+        <v>0.8611111111111096</v>
       </c>
       <c r="AB88">
         <v>8000</v>
@@ -8382,7 +8382,7 @@
         <v>117</v>
       </c>
       <c r="AA92">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB92">
         <v>8000</v>
@@ -8465,7 +8465,7 @@
         <v>117</v>
       </c>
       <c r="AA93">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB93">
         <v>8000</v>
@@ -8548,7 +8548,7 @@
         <v>117</v>
       </c>
       <c r="AA94">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB94">
         <v>8000</v>
@@ -8631,7 +8631,7 @@
         <v>117</v>
       </c>
       <c r="AA95">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB95">
         <v>8000</v>
@@ -8714,7 +8714,7 @@
         <v>117</v>
       </c>
       <c r="AA96">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB96">
         <v>8000</v>
@@ -8797,7 +8797,7 @@
         <v>117</v>
       </c>
       <c r="AA97">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB97">
         <v>8000</v>
@@ -8880,7 +8880,7 @@
         <v>117</v>
       </c>
       <c r="AA98">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB98">
         <v>8000</v>
@@ -8963,7 +8963,7 @@
         <v>117</v>
       </c>
       <c r="AA99">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB99">
         <v>8000</v>
@@ -9046,7 +9046,7 @@
         <v>117</v>
       </c>
       <c r="AA100">
-        <v>10</v>
+        <v>16.86342592592595</v>
       </c>
       <c r="AB100">
         <v>8000</v>
@@ -9129,7 +9129,7 @@
         <v>117</v>
       </c>
       <c r="AA101">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB101">
         <v>8000</v>
@@ -9212,7 +9212,7 @@
         <v>117</v>
       </c>
       <c r="AA102">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB102">
         <v>8000</v>
@@ -9295,7 +9295,7 @@
         <v>117</v>
       </c>
       <c r="AA103">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB103">
         <v>8000</v>
@@ -9378,7 +9378,7 @@
         <v>117</v>
       </c>
       <c r="AA104">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB104">
         <v>8000</v>
@@ -9461,7 +9461,7 @@
         <v>117</v>
       </c>
       <c r="AA105">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB105">
         <v>8000</v>
@@ -9544,7 +9544,7 @@
         <v>117</v>
       </c>
       <c r="AA106">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AB106">
         <v>8000</v>
@@ -9627,7 +9627,7 @@
         <v>117</v>
       </c>
       <c r="AA107">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB107">
         <v>8000</v>
@@ -9710,7 +9710,7 @@
         <v>117</v>
       </c>
       <c r="AA108">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB108">
         <v>8000</v>
@@ -9793,7 +9793,7 @@
         <v>117</v>
       </c>
       <c r="AA109">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB109">
         <v>8000</v>
@@ -10125,7 +10125,7 @@
         <v>117</v>
       </c>
       <c r="AA113">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AB113">
         <v>8000</v>
@@ -10208,7 +10208,7 @@
         <v>117</v>
       </c>
       <c r="AA114">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AB114">
         <v>8000</v>
@@ -10291,7 +10291,7 @@
         <v>117</v>
       </c>
       <c r="AA115">
-        <v>10</v>
+        <v>19.36574074074073</v>
       </c>
       <c r="AB115">
         <v>8000</v>
@@ -12366,7 +12366,7 @@
         <v>117</v>
       </c>
       <c r="AA140">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB140">
         <v>8000</v>
@@ -12449,7 +12449,7 @@
         <v>117</v>
       </c>
       <c r="AA141">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB141">
         <v>8000</v>
@@ -12532,7 +12532,7 @@
         <v>117</v>
       </c>
       <c r="AA142">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB142">
         <v>8000</v>
@@ -12864,7 +12864,7 @@
         <v>117</v>
       </c>
       <c r="AA146">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB146">
         <v>8000</v>
@@ -12947,7 +12947,7 @@
         <v>117</v>
       </c>
       <c r="AA147">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB147">
         <v>8000</v>
@@ -13030,7 +13030,7 @@
         <v>117</v>
       </c>
       <c r="AA148">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB148">
         <v>8000</v>
@@ -13119,7 +13119,7 @@
         <v>117</v>
       </c>
       <c r="AA149">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB149">
         <v>8000</v>
@@ -13202,7 +13202,7 @@
         <v>117</v>
       </c>
       <c r="AA150">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB150">
         <v>8000</v>
@@ -13285,7 +13285,7 @@
         <v>117</v>
       </c>
       <c r="AA151">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB151">
         <v>8000</v>
@@ -13368,7 +13368,7 @@
         <v>117</v>
       </c>
       <c r="AA152">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB152">
         <v>8000</v>
@@ -13457,7 +13457,7 @@
         <v>117</v>
       </c>
       <c r="AA153">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB153">
         <v>8000</v>
@@ -13546,7 +13546,7 @@
         <v>117</v>
       </c>
       <c r="AA154">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB154">
         <v>8000</v>
